--- a/test_data/Treaties MLIData/Treaties MLIData_Test_Cases.xlsx
+++ b/test_data/Treaties MLIData/Treaties MLIData_Test_Cases.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MLI Data loaded at https://regplus.kaz.com.bd/wta/MLIData?sort=jurisdiction%3Aasc with its table pre-rendered (107 rows, expected columns).</t>
+          <t>MLI Data loaded at https://regplusrc.reganalytics.com/wta/MLIData?sort=jurisdiction%3Aasc with its table pre-rendered (107 rows, expected columns).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">

--- a/test_data/Treaties MLIData/Treaties MLIData_Test_Cases.xlsx
+++ b/test_data/Treaties MLIData/Treaties MLIData_Test_Cases.xlsx
@@ -44,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,250 +553,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MLI Data loaded at https://regplusrc.reganalytics.com/wta/MLIData?sort=jurisdiction%3Aasc with its table pre-rendered (107 rows, expected columns).</t>
+          <t>MLI Data did not load as expected (url_ok=True, headers=[], rows=0).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] MLI Data table pre-renders with 8 expected columns and &gt;100 rows</t>
+          <t>[FAIL] MLI Data table pre-renders with 8 expected columns and &gt;100 rows</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>MLIData_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Treaties MLIData</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Default '?sort=jurisdiction:asc' URL yields an alphabetically-first row</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Loading /wta/MLIData?sort=jurisdiction%3Aasc must show 'Albania' as the first jurisdiction in the table (alphabetically first among signatories).</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>sort=jurisdiction:asc</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open MLI Data with the asc sort param
-2. Verify the first row's jurisdiction is 'Albania'</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Loading /wta/MLIData?sort=jurisdiction%3Aasc must show 'Albania' as the first jurisdiction in the table (alphabetically first among signatories).</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>The first row under the default ascending sort correctly starts with 'Albania'.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] First row under ascending sort is 'Albania'</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>MLIData_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Treaties MLIData</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Jurisdiction' column header toggles sort direction</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the sortable 'Jurisdiction' column header on a table loaded ascending must flip the URL's sort param to 'jurisdiction:desc' and change the first visible row from 'Albania' to the alphabetically-last jurisdiction.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on MLI Data (ascending sort).</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open MLI Data (asc)
-2. Click the 'Jurisdiction' column header
-3. Verify the URL sort param flips to desc and the first row changes</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the sortable 'Jurisdiction' column header on a table loaded ascending must flip the URL's sort param to 'jurisdiction:desc' and change the first visible row from 'Albania' to the alphabetically-last jurisdiction.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Jurisdiction' header flipped the sort to descending; the first row changed from 'Albania\n\t\n28 May 2019\n\t\n22 September 2020\n\t\n01 January 2021\n' to 'Zambia\nThis country is a member of the OECD’s Inclusive Fram'.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Clicking the Jurisdiction header flips the URL sort param and reorders the table</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>MLIData_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Treaties MLIData</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MLI Data has no jurisdiction selection panel, unlike the other Treaties pages</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed live that MLI Data has no left 'Jurisdictions' panel and no 'Search countries' box - the 'Select Jurisdiction' heading and country search input used on the other 4 Treaties pages must both be ABSENT here.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on MLI Data.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open MLI Data
-2. Verify no 'Select Jurisdiction' heading and no country search box are present</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed live that MLI Data has no left 'Jurisdictions' panel and no 'Search countries' box - the 'Select Jurisdiction' heading and country search input used on the other 4 Treaties pages must both be ABSENT here.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MLI Data correctly has no jurisdiction-selection heading or country search box, confirming it is not jurisdiction-gated like the other 4 Treaties pages.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] No jurisdiction-selection UI is present on MLI Data</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>MLIData_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Treaties MLIData</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The Albania row shows its known MLI signature and entry-into-force dates</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>The 'Albania' row must show '28 May 2019' (Signature) and '01 January 2021' (Entry into Force).</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on MLI Data.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Jurisdiction: Albania</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open MLI Data
-2. Verify the Albania row contains its known dates</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>The 'Albania' row must show '28 May 2019' (Signature) and '01 January 2021' (Entry into Force).</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>The Albania row correctly shows its known Signature (28 May 2019) and Entry into Force (01 January 2021) dates.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Albania row shows its known Signature and Entry into Force dates</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
